--- a/analysis/tables/bloom-1b1.xlsx
+++ b/analysis/tables/bloom-1b1.xlsx
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7871438062570995</v>
+        <v>0.6349626703807271</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1946830407481376</v>
+        <v>-0.1579496631228065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.787x - 0.195</t>
+          <t>y = 0.635x - 0.158</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -553,10 +553,10 @@
         <v>0.07949844646981874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2473284286817466</v>
+        <v>0.2487542504319176</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5924607655089619</v>
+        <v>0.4770130072579205</v>
       </c>
       <c r="K3" t="n">
         <v>0.1230335942309437</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.780385435649719</v>
+        <v>0.6294678844678193</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.03514352565799161</v>
+        <v>-0.1493440040719486</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.780x - 0.035</t>
+          <t>y = 0.629x - 0.149</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.756115557185981</v>
+        <v>0.7187664039301185</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07823574883004092</v>
+        <v>0.0793933368200274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04503354887541239</v>
+        <v>0.2372543663577225</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7452419099917273</v>
+        <v>0.4801238803958707</v>
       </c>
       <c r="K4" t="n">
         <v>0.1230335942309437</v>
